--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMProcedure.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:53:12+00:00</t>
+    <t>2026-08-20T15:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -431,7 +431,7 @@
     <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis|20260716085852</t>
   </si>
   <si>
     <t>FRLMEntry.header.status</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMProcedure.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T15:08:45+00:00</t>
+    <t>2026-08-20T15:24:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMProcedure.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T15:24:46+00:00</t>
+    <t>2026-08-21T08:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMProcedure.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T08:13:05+00:00</t>
+    <t>2026-08-23T21:45:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMProcedure.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-23T21:45:18+00:00</t>
+    <t>2026-08-24T13:13:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMProcedure.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMProcedure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="176">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T13:13:01+00:00</t>
+    <t>2026-08-25T11:34:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -469,115 +469,11 @@
     <t>FRLMProcedure.procedureDate[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {organization-period|5.3.0}
-</t>
-  </si>
-  <si>
-    <t>Période de l'acte</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>FRLMProcedure.procedureDate[x].id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>FRLMProcedure.procedureDate[x].extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>FRLMProcedure.procedureDate[x].url</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>FRLMProcedure.procedureDate[x].value[x]</t>
-  </si>
-  <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>FRLMProcedure.procedureDate[x].procedureDateDateTime</t>
-  </si>
-  <si>
-    <t>Date de début de l'acte</t>
-  </si>
-  <si>
-    <t>FRLMProcedure.procedureDate[x].procedureDatePeriod</t>
-  </si>
-  <si>
-    <t>Date de fin de l'acte</t>
+    <t>dateTime
+Period</t>
+  </si>
+  <si>
+    <t>Période de l'acte. Si Period : porte la date de début et de fin de l'acte.</t>
   </si>
   <si>
     <t>FRLMProcedure.priority</t>
@@ -660,6 +556,10 @@
   </si>
   <si>
     <t>FRLMProcedure.note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
   </si>
   <si>
     <t>Commentaire</t>
@@ -964,13 +864,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ37"/>
+  <dimension ref="A1:AJ31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.44921875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="49.44921875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
@@ -995,10 +895,10 @@
     <col min="26" max="26" width="67.11328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="47.5234375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.63671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -3111,15 +3011,15 @@
         <v>72</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>149</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3142,13 +3042,13 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3175,10 +3075,10 @@
         <v>72</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="Z22" t="s" s="2">
         <v>72</v>
@@ -3199,7 +3099,7 @@
         <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>73</v>
@@ -3216,21 +3116,21 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>156</v>
+        <v>72</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>72</v>
@@ -3242,17 +3142,15 @@
         <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>72</v>
@@ -3289,39 +3187,39 @@
         <v>72</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>161</v>
+        <v>72</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>163</v>
+        <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>149</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3329,7 +3227,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>78</v>
@@ -3344,17 +3242,15 @@
         <v>72</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>72</v>
@@ -3379,10 +3275,10 @@
         <v>72</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>72</v>
+        <v>157</v>
       </c>
       <c r="Z24" t="s" s="2">
         <v>72</v>
@@ -3403,10 +3299,10 @@
         <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>78</v>
@@ -3420,10 +3316,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3446,13 +3342,13 @@
         <v>72</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>172</v>
+        <v>130</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3503,7 +3399,7 @@
         <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>73</v>
@@ -3515,15 +3411,15 @@
         <v>72</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>176</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3534,7 +3430,7 @@
         <v>73</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>72</v>
@@ -3546,13 +3442,13 @@
         <v>72</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3603,13 +3499,13 @@
         <v>72</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>72</v>
@@ -3620,10 +3516,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3646,13 +3542,13 @@
         <v>72</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3703,7 +3599,7 @@
         <v>72</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>73</v>
@@ -3720,10 +3616,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3734,7 +3630,7 @@
         <v>73</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>72</v>
@@ -3749,10 +3645,10 @@
         <v>130</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3779,10 +3675,10 @@
         <v>72</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>72</v>
@@ -3803,13 +3699,13 @@
         <v>72</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>72</v>
@@ -3820,10 +3716,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3834,7 +3730,7 @@
         <v>73</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>72</v>
@@ -3846,13 +3742,13 @@
         <v>72</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>185</v>
+        <v>102</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3903,13 +3799,13 @@
         <v>72</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>72</v>
@@ -3920,10 +3816,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3934,7 +3830,7 @@
         <v>73</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>72</v>
@@ -3946,13 +3842,13 @@
         <v>72</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3979,10 +3875,10 @@
         <v>72</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>133</v>
+        <v>72</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>189</v>
+        <v>72</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>72</v>
@@ -4003,13 +3899,13 @@
         <v>72</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>72</v>
@@ -4020,10 +3916,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4046,13 +3942,13 @@
         <v>72</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>130</v>
+        <v>174</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4103,7 +3999,7 @@
         <v>72</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>73</v>
@@ -4115,606 +4011,6 @@
         <v>72</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E32" s="2"/>
-      <c r="F32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K32" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-      <c r="P32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q32" s="2"/>
-      <c r="R32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K33" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-      <c r="P33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q33" s="2"/>
-      <c r="R33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K34" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-      <c r="P34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q34" s="2"/>
-      <c r="R34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K35" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
-      <c r="P35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q35" s="2"/>
-      <c r="R35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K36" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-      <c r="P36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q36" s="2"/>
-      <c r="R36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E37" s="2"/>
-      <c r="F37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K37" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
-      <c r="P37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q37" s="2"/>
-      <c r="R37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMProcedure.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T11:34:21+00:00</t>
+    <t>2026-08-25T11:56:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMProcedure.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T11:56:50+00:00</t>
+    <t>2026-08-25T20:08:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/StructureDefinition-FRLMProcedure.xlsx
+++ b/fix-target-codes-and-display/ig/StructureDefinition-FRLMProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T20:08:46+00:00</t>
+    <t>2026-08-31T08:09:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
